--- a/submission/COMAVI_v7.15_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S2_Table.xlsx
@@ -590,7 +590,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1858,10 +1857,8 @@
           <t>6.78</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O16" t="n">
+        <v>-0.03</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1948,10 +1945,8 @@
           <t>-0.16</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O17" t="n">
+        <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -2038,10 +2033,8 @@
           <t>-0.26</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O18" t="n">
+        <v>-0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2398,10 +2391,8 @@
           <t>0.27</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O22" t="n">
+        <v>-0.06</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2758,10 +2749,8 @@
           <t>0.80</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O26" t="n">
+        <v>-0.02</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2848,10 +2837,8 @@
           <t>-0.43</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O27" t="n">
+        <v>-0.14</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3298,10 +3285,8 @@
           <t>-2.29</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O32" t="n">
+        <v>0.06</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3388,10 +3373,8 @@
           <t>-0.25</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O33" t="n">
+        <v>0.06</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3478,10 +3461,8 @@
           <t>0.12</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O34" t="n">
+        <v>-0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3658,10 +3639,8 @@
           <t>-1.20</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O36" t="n">
+        <v>-0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3748,10 +3727,8 @@
           <t>1.17</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O37" t="n">
+        <v>-0.27</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4198,10 +4175,8 @@
           <t>5.38</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O42" t="n">
+        <v>0.96</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -4288,10 +4263,8 @@
           <t>15.26</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O43" t="n">
+        <v>0.96</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -4378,10 +4351,8 @@
           <t>2.04</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O44" t="n">
+        <v>0.96</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -4468,10 +4439,8 @@
           <t>2.89</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O45" t="n">
+        <v>0.97</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -4558,10 +4527,8 @@
           <t>-0.03</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O46" t="n">
+        <v>0.96</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4828,10 +4795,8 @@
           <t>2.32</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O49" t="n">
+        <v>-0.39</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -4918,10 +4883,8 @@
           <t>0.26</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O50" t="n">
+        <v>0</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -5098,10 +5061,8 @@
           <t>10.69</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O52" t="n">
+        <v>0.22</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -5188,10 +5149,8 @@
           <t>0.75</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O53" t="n">
+        <v>0</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -5278,10 +5237,8 @@
           <t>0.14</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O54" t="n">
+        <v>0</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -5458,10 +5415,8 @@
           <t>0.47</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O56" t="n">
+        <v>0</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -5908,10 +5863,8 @@
           <t>4.46</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O61" t="n">
+        <v>0</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -5998,10 +5951,8 @@
           <t>1.25</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="O62" t="n">
+        <v>0</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -6229,7 +6180,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6408,7 +6358,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6525,7 +6474,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6722,7 +6670,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6859,7 +6806,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S2_Table.xlsx
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -6180,6 +6180,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6219,13 +6220,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -6243,20 +6244,20 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quantitative functional readout coupled to the axis.</t>
+          <t>Quantitative functional readout coupled to the axis. The one stabilizing expectation is the SMAD4 I500V binding axis.</t>
         </is>
       </c>
     </row>
@@ -6267,10 +6268,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>

--- a/submission/COMAVI_v7.15_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S2_Table.xlsx
@@ -6180,7 +6180,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6520,27 +6519,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Any pLDDT-passing interface</t>
+          <t>Any pLDDT-passing interface contact</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15/2</t>
+          <t>15/6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7/23</t>
+          <t>7/18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.720</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6550,12 +6549,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6567,37 +6566,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14/3</t>
+          <t>14/7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>0.560</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.5222</t>
         </is>
       </c>
     </row>
@@ -6609,37 +6608,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/0</t>
+          <t>17/4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>0.586</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0095</t>
+          <t>0.1651</t>
         </is>
       </c>
     </row>
@@ -6701,27 +6700,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Primary 57-variant graded cohort</t>
+          <t>Primary 56-variant graded cohort</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.0/57 = 0.719</t>
+          <t>37.0/56 = 0.661</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19/25 = 0.760</t>
+          <t>19/26 = 0.731</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58/77 = 0.753</t>
+          <t>56/77 = 0.727</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>92/124 = 0.742</t>
+          <t>86/123 = 0.699</t>
         </is>
       </c>
     </row>
@@ -6738,29 +6737,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19/26 = 0.731</t>
+          <t>19/27 = 0.704</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>58/78 = 0.744</t>
+          <t>56/78 = 0.718</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>92/125 = 0.736</t>
+          <t>86/124 = 0.694</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Include BRCA1 R1699L/Q in rubric-only sensitivity</t>
+          <t>Include BRCA1 R1699L/Q in grading</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>43.0/59 = 0.729</t>
+          <t>39.0/58 = 0.672</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/submission/COMAVI_v7.15_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S2_Table.xlsx
@@ -590,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5136,7 +5137,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Le Goff et al. 2012 [44]</t>
+          <t>Le Goff et al. 2012 [45]</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5224,7 +5225,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Le Goff et al. 2012 [44]</t>
+          <t>Le Goff et al. 2012 [45]</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5670,7 +5671,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Elliott et al. 2000 [46]</t>
+          <t>Elliott et al. 2000 [48]</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5850,7 +5851,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Stebbins et al. 1999 [49]</t>
+          <t>Stebbins et al. 1999 [51]</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6180,6 +6181,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6358,6 +6360,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6474,6 +6477,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6670,6 +6674,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -6806,6 +6811,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/submission/COMAVI_v7.15_SI/S2_Table.xlsx
+++ b/submission/COMAVI_v7.15_SI/S2_Table.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Agreement 1.0/1.5/2.0/2.5/Bound</t>
+          <t>Agreement 1.0/1.5/2.0/2.5/2.9-2.9-3.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
